--- a/labs/day1/d1_end_eda_template.xlsx
+++ b/labs/day1/d1_end_eda_template.xlsx
@@ -953,7 +953,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>00_코드표 · 결제조건 표기 → 정본 코드 7개 (Lab2)</t>
+          <t>00_코드표 · 결제조건 표기 → 정본 코드 7개 (Step 5)</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>01_보고서신호 · AI가 찾은 위험 신호를 원문으로 확인하기 (Lab1)</t>
+          <t>01_보고서신호 · AI가 찾은 위험 신호를 원문으로 확인하기 (Step 2)</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2418,7 @@
     <row r="6" ht="31" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>예시 ▶ 슬라이드 23 형식(5필드)</t>
+          <t>예시 ▶ 슬라이드 31 형식(5필드)</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
@@ -3167,7 +3167,7 @@
     <dataValidation sqref="B46:B48" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="목록에서 고르기" error="목록(▼)에서 골라 주세요." promptTitle="계속기업 문구 상태" prompt="의문 제기 / 해소 기재 / 언급 없음 — 부정·해소 표현(no longer 등)은 문장 전체를 읽고 고릅니다." type="list" errorStyle="stop">
       <formula1>"의문 제기,해소 기재,언급 없음"</formula1>
     </dataValidation>
-    <dataValidation sqref="D68:D70" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="목록에서 고르기" error="목록(▼)에서 골라 주세요." promptTitle="4단계 판정" prompt="검증가능 · 자료기반추정 · 거짓 · 검증불가(슬라이드 28)." type="list" errorStyle="stop">
+    <dataValidation sqref="D68:D70" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="목록에서 고르기" error="목록(▼)에서 골라 주세요." promptTitle="4단계 판정" prompt="검증가능 · 자료기반추정 · 거짓 · 검증불가(슬라이드 41)." type="list" errorStyle="stop">
       <formula1>"검증가능,자료기반추정,거짓,검증불가"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3213,14 +3213,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>02_비율검증 · AI가 계산한 재무비율 검산 (Lab1)</t>
+          <t>02_비율검증 · AI가 계산한 재무비율 검산 (Step 3)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="35" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AI(P1-2)가 보여 준 분자·분모와 결과를 노란 칸에 적으면 회색 칸이 '내 계산'과 '차이율'을 자동으로 냅니다. 기준값은 iRobot = real_buyers_ratios.csv(SEC), Halden = 강사 정답 공개 뒤에 적고, K열에서 4단계 판정을 고릅니다. 매출채권회전일은 L열 '기간 일수'(연간 365)로 계산하고, 차이의 원인은 M열 메모에 적습니다.</t>
+          <t>AI(P1-2)가 보여 준 분자·분모와 결과를 노란 칸에 적으면 회색 칸이 '내 계산'과 '차이율'을 자동으로 냅니다. 기준값은 iRobot = real_buyers_ratios.csv(SEC), Halden = 14:20 강사 정답 공개 때 적고, K열에서 4단계 판정을 고릅니다. 매출채권회전일은 L열 '기간 일수'(연간 365)로 계산하고, 차이의 원인은 M열 메모에 적습니다.</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
     <row r="31" ht="19.5" customHeight="1">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>숫자 검증 4단계(슬라이드 28)</t>
+          <t>숫자 검증 4단계(슬라이드 41)</t>
         </is>
       </c>
     </row>
@@ -4149,14 +4149,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>03_EDA · 바이어 데이터 진단 · 요약 · 검산 (Lab2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
+          <t>03_EDA · 바이어 데이터 진단 · 요약 · 검산 (Step 4 · Step 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="35" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>① P1-3 진단 결과(이상한 점 목록) ② P1-4 요약표·차트·코드 ③ AI 숫자와 내 피벗 숫자 대조 ④ 인사이트 3개를 차례로 채웁니다. AI에게는 진단만 시키고, 데이터를 고치게 하지 않습니다.</t>
+          <t>①② Step 4: P1-3 진단 결과(이상한 점 목록) · P1-4 요약표·차트·코드와 AI 숫자 ③④ Step 6: AI 숫자와 내 피벗 숫자 대조 · 인사이트 2–3개를 차례로 채웁니다. AI에게는 진단만 시키고, 데이터를 고치게 하지 않습니다.</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
     <row r="72">
       <c r="A72" s="18" t="inlineStr">
         <is>
-          <t>④ 인사이트 3개 — 숫자가 들어간 한 문장으로</t>
+          <t>④ 인사이트 2–3개 — 숫자가 들어간 한 문장으로(근거 피벗 · 다음 행동)</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5152,7 @@
     <dataValidation sqref="G7:G21" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="목록에서 고르기" error="목록(▼)에서 골라 주세요." promptTitle="원본에서 확인" prompt="AI가 말한 이상한 점을 원본 파일에서 직접 찾아봤으면 ✔, 원본에 없으면 ✘." type="list" errorStyle="stop">
       <formula1>"✔,✘"</formula1>
     </dataValidation>
-    <dataValidation sqref="B61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="목록에서 고르기" error="목록(▼)에서 골라 주세요." promptTitle="코드 받기" prompt="'사용한 코드와 계산식을 보여 줘' — 이 한 문장이 검증 가능성을 만듭니다(슬라이드 27)." type="list" errorStyle="stop">
+    <dataValidation sqref="B61" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="목록에서 고르기" error="목록(▼)에서 골라 주세요." promptTitle="코드 받기" prompt="'사용한 코드와 계산식을 보여 줘' — 이 한 문장이 검증 가능성을 만듭니다(슬라이드 39)." type="list" errorStyle="stop">
       <formula1>"예,아니오"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5202,14 +5202,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_피벗 · 피벗 3개 + 차트 (Lab2)</t>
+          <t>04_피벗 · 피벗 + 100% 누적 막대 (Step 5) — 오늘 결과물 'EDA 시각화 차트'</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>buyers 시트의 표(tbl_buyers)로 피벗 테이블 3개와 차트를 이 시트의 정해진 자리에 만듭니다. 피벗을 만들 때 '기존 워크시트'를 고르고, 위치 칸에는 아래 ▼ 표시 바로 밑 칸을 클릭하세요.</t>
+          <t>buyers 시트의 표(tbl_buyers)로 피벗①·② + 차트(필수)와 피벗③(다 했으면)을 이 시트의 정해진 자리에 만듭니다. 피벗을 만들 때 '기존 워크시트'를 고르고, 위치 칸에는 아래 ▼ 표시 바로 밑 칸을 클릭하세요.</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5223,7 @@
     <row r="5">
       <c r="A5" s="18" t="inlineStr">
         <is>
-          <t>만드는 순서(피벗 3개 공통)</t>
+          <t>만드는 순서(피벗 공통)</t>
         </is>
       </c>
     </row>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>값 상자의 '개수: buyer_id' 클릭 → [값 필드 설정] → [값 표시 형식] 탭 → '행 합계 비율' → [확인]</t>
+          <t>값 상자의 '개수: buyer_id' 클릭 → [값 필드 설정] → [값 표시 형식] 탭 → '행 합계 비율' → [확인] · 업종 보기(1분): industry를 [필터] 상자로 → 업종을 바꿔 가며 차트를 본 뒤 (모두)로 되돌리기</t>
         </is>
       </c>
       <c r="G13" s="6" t="n"/>
@@ -5472,10 +5472,10 @@
       <c r="P14" s="6" t="n"/>
       <c r="Q14" s="7" t="n"/>
     </row>
-    <row r="15" ht="19.5" customHeight="1">
+    <row r="15" ht="34" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>③ 권역 × 보험 가입</t>
+          <t>③ 권역 × 보험 가입(다 했으면)</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -6004,7 +6004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6014,26 +6014,27 @@
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>05_변수정의서 · 숫자 하나에도 7가지 약속 (선택 과제)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="35" customHeight="1">
+          <t>05_변수정의서 · 숫자 하나에도 7가지 약속 (오늘 결과물 · Step 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="50" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>(선택) 변수마다 변수·정의·공식·단위·출처·기준일·주의 7칸을 적습니다. 위 3줄은 슬라이드 34와 같습니다. 주황색 '빈칸 채우기' 칸을 채워 보세요 — AI에게 계산을 시킬 때 이 7칸을 같이 주고, 내일(Day2) 데이터 사전의 출발점이 됩니다.</t>
+          <t>오늘 결과물 '변수 정의서'입니다(교수계획서 1일차 결과물). 변수마다 변수·정의·공식·단위·출처·기준일·주의 7칸 — 위 4줄은 슬라이드 38과 같습니다. 제출 최소 기준(필수): ① op_margin 행의 주황 칸 2개(정의·주의) ② 주황 칸이 있는 다른 행 하나를 골라 그 행의 주황 칸 모두(예: max_dpd_days의 단위·기준일·주의) — H열 표시. 나머지 주황 칸은 선택입니다. AI에게 계산을 시킬 때 이 7칸을 같이 주고, 내일(2일차) 데이터 사전의 출발점이 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>주황 칸 = 빈칸 채우기 · 노란 칸 = 내가 추가할 변수 · 저장: [파일] → [다른 이름으로 저장] → d1_end_eda__T조-번호.xlsx</t>
+          <t>주황 칸 = 빈칸 채우기 · H열 = 제출 기준 · 노란 칸 = 내가 추가할 변수 · 저장: [파일] → [다른 이름으로 저장] → d1_end_eda__T조-번호.xlsx</t>
         </is>
       </c>
     </row>
@@ -6073,8 +6074,13 @@
           <t>주의</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>제출 기준(결과물)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>current_ratio (유동비율)</t>
@@ -6110,8 +6116,13 @@
           <t>업종별 차이</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>채워져 있음 — 읽고 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>debt_to_equity (부채비율)</t>
@@ -6147,8 +6158,13 @@
           <t>자본이 음수면 해석 불가 → 따로 표시</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>채워져 있음 — 읽고 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>dso_days (매출채권회전일)</t>
@@ -6184,8 +6200,13 @@
           <t>분기 매출을 쓰면 4배 왜곡</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>채워져 있음 — 읽고 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>op_margin (영업이익률)</t>
@@ -6219,6 +6240,11 @@
       <c r="G9" s="52" t="inlineStr">
         <is>
           <t>빈칸 채우기</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>필수 ① — 주황 칸 2개</t>
         </is>
       </c>
     </row>
@@ -6258,6 +6284,11 @@
           <t>빈칸 채우기</t>
         </is>
       </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>필수 ② 후보 — 이 중 1행</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
@@ -6295,8 +6326,13 @@
           <t>빈칸 채우기</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>필수 ② 후보 — 이 중 1행</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>dpd_num (연체일수·숫자)</t>
@@ -6330,6 +6366,11 @@
       <c r="G12" s="52" t="inlineStr">
         <is>
           <t>빈칸 채우기</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>필수 ② 후보 — 이 중 1행</t>
         </is>
       </c>
     </row>
@@ -6369,8 +6410,13 @@
           <t>바이어 단위(가장 오래된 1건) 구간 — 인보이스 단위 에이징과 다르다</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>필수 ② 후보 — 이 중 1행</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>is_overdue (연체 여부)</t>
@@ -6404,6 +6450,11 @@
       <c r="G14" s="52" t="inlineStr">
         <is>
           <t>빈칸 채우기</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>필수 ② 후보 — 이 중 1행</t>
         </is>
       </c>
     </row>
@@ -6443,8 +6494,13 @@
           <t>빈칸 채우기</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>필수 ② 후보 — 이 중 1행</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>ar_balance (매출채권 잔액)</t>
@@ -6478,6 +6534,11 @@
       <c r="G16" s="52" t="inlineStr">
         <is>
           <t>빈칸 채우기</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>필수 ② 후보 — 이 중 1행</t>
         </is>
       </c>
     </row>
@@ -6517,6 +6578,11 @@
           <t>빈칸 채우기</t>
         </is>
       </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>필수 ② 후보 — 이 중 1행</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="34" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
@@ -6552,6 +6618,11 @@
       <c r="G18" s="52" t="inlineStr">
         <is>
           <t>빈칸 채우기</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>필수 ② 후보 — 이 중 1행</t>
         </is>
       </c>
     </row>
@@ -6598,8 +6669,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A2:H2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.55" bottom="0.55" header="0.25" footer="0.25"/>
@@ -6638,14 +6709,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>06_현안정의서 · 결제방식별 리스크 현안 (Lab3)</t>
+          <t>06_현안정의서 · 결제방식별 리스크 현안 (Step 7)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="35" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Lab2 피벗①의 숫자를 결제방식별로 옮겨 적고(L/C = LC_SIGHT + LC_USANCE), AI 초안(P1-5)을 요약합니다. 근거 없는 수치·규정은 지우고 '확인 필요' 칸으로 옮긴 뒤, 최종 문장은 사람이 씁니다.</t>
+          <t>Step 5 피벗①의 숫자를 결제방식별로 옮겨 적고(L/C = LC_SIGHT + LC_USANCE), AI 초안(P1-5)을 요약합니다. 근거 없는 수치·규정은 지우고 '확인 필요' 칸으로 옮긴 뒤, 최종 문장은 사람이 씁니다.</t>
         </is>
       </c>
     </row>
@@ -6864,14 +6935,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>07_내AX프로젝트 · AX 문제 정의 캔버스 + 과업 선정 3기준 (Lab3)</t>
+          <t>07_내AX프로젝트 · AX 문제 정의 캔버스 + 과업 선정 3기준 (Step 8 · 8교시)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="35" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AI 질문형 코치(P1-6)가 한 번에 한 질문씩 묻고 내가 답합니다. 답한 내용을 7칸에 적고, 후보 과업마다 3기준 점수와 근거 한 줄을 씁니다. 고객사 실명·담당자 이름·계좌는 쓰지 않습니다.</t>
+          <t>Step 8: AI 질문형 코치(P1-6)가 한 번에 한 질문씩 묻고 내가 답합니다. 답한 내용을 7칸에 적고 옆 사람과 검증합니다. 후보 과업마다 3기준 점수와 근거 한 줄은 8교시(17:10, 슬라이드 60)에 씁니다. 고객사 실명·담당자 이름·계좌는 쓰지 않습니다.</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6982,7 @@
     <row r="8">
       <c r="A8" s="18" t="inlineStr">
         <is>
-          <t>AX 문제 정의 캔버스 (7칸) — 슬라이드 42와 같은 칸</t>
+          <t>AX 문제 정의 캔버스 (7칸) — 슬라이드 60과 같은 칸</t>
         </is>
       </c>
     </row>
@@ -7044,7 +7115,7 @@
     <row r="17">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>과업 선정 3기준 · 각 1–5점 — 후보 과업마다 매기고, 점수마다 근거 한 줄</t>
+          <t>과업 선정 3기준 · 각 1–5점 — 8교시(17:10)에 후보 과업마다 매기고, 점수마다 근거 한 줄</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7214,7 @@
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>옆 사람 검증(10분) — 서로 캔버스를 바꿔 보고 딱 하나만 묻기: "무엇을 놓치면 비싼가?"</t>
+          <t>옆 사람 검증(Step 8, 4분) — 서로 캔버스를 바꿔 보고 딱 하나만 묻기: "무엇을 놓치면 비싼가?"</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7273,7 @@
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>다음 단계 — Day2에 가져올 데이터 목록(오늘 과제: 무엇이 · 어디에 · 얼마나 민감한가)</t>
+          <t>다음 단계 — 2일차에 가져올 데이터 목록(오늘 과제: 무엇이 · 어디에 · 얼마나 민감한가)</t>
         </is>
       </c>
     </row>
@@ -7283,7 +7354,7 @@
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>담당자 이름·이메일·계좌는 지웁니다(개인정보). 법인 재무 숫자는 개인정보가 아닙니다. 회사 보안 규정이 있으면 그것이 먼저입니다(슬라이드 35).</t>
+          <t>담당자 이름·이메일·계좌는 지웁니다(개인정보). 법인 재무 숫자는 개인정보가 아닙니다. 회사 보안 규정이 있으면 그것이 먼저입니다(슬라이드 47).</t>
         </is>
       </c>
     </row>
